--- a/data/trans_orig/P16A08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A08-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25471</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26329</t>
+          <t>25860</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23862</t>
+          <t>24781</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47757</t>
+          <t>46474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>468473</t>
+          <t>468593</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484251</t>
+          <t>484024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>441160</t>
+          <t>441629</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>456836</t>
+          <t>456263</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>913796</t>
+          <t>915079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>937691</t>
+          <t>936772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30437</t>
+          <t>29609</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17628</t>
+          <t>17097</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>39132</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31648</t>
+          <t>31951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59518</t>
+          <t>60253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>705052</t>
+          <t>705880</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>724203</t>
+          <t>724788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>586639</t>
+          <t>586362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607866</t>
+          <t>608397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1301464</t>
+          <t>1300729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1329334</t>
+          <t>1329031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>18992</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40765</t>
+          <t>39137</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>29109</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>53351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616559</t>
+          <t>617718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631066</t>
+          <t>631132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>648979</t>
+          <t>650607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>670618</t>
+          <t>670752</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1271781</t>
+          <t>1274043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1298201</t>
+          <t>1298285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>19979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25543</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17840</t>
+          <t>18047</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39371</t>
+          <t>41565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>497791</t>
+          <t>499168</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>514880</t>
+          <t>514429</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>490099</t>
+          <t>490068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>506161</t>
+          <t>506925</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>995418</t>
+          <t>993224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1016949</t>
+          <t>1016742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19413</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30232</t>
+          <t>30561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20484</t>
+          <t>19108</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43448</t>
+          <t>41778</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>367297</t>
+          <t>367149</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>381521</t>
+          <t>381619</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>373754</t>
+          <t>373425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>391669</t>
+          <t>391582</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>747248</t>
+          <t>748918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>770212</t>
+          <t>771588</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>24489</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31966</t>
+          <t>31873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281899</t>
+          <t>280209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290773</t>
+          <t>290758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>318267</t>
+          <t>318445</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>333555</t>
+          <t>333708</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>603551</t>
+          <t>603644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>621158</t>
+          <t>621736</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22027</t>
+          <t>23387</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>198549</t>
+          <t>198464</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208176</t>
+          <t>208247</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>316609</t>
+          <t>317607</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330538</t>
+          <t>330644</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>521764</t>
+          <t>520404</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>537320</t>
+          <t>537129</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61545</t>
+          <t>61076</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>98468</t>
+          <t>96429</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110742</t>
+          <t>110391</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>154949</t>
+          <t>157218</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>180513</t>
+          <t>182254</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>242450</t>
+          <t>242954</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3177057</t>
+          <t>3179096</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3213980</t>
+          <t>3214449</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3224248</t>
+          <t>3221979</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3268455</t>
+          <t>3268806</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6412272</t>
+          <t>6411768</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6474209</t>
+          <t>6472468</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11375</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>28148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18875</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39866</t>
+          <t>39258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33549</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59157</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424409</t>
+          <t>424957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>441730</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>389473</t>
+          <t>390081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>410464</t>
+          <t>410141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>823288</t>
+          <t>821470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>848896</t>
+          <t>848397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40101</t>
+          <t>39245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27305</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50312</t>
+          <t>51873</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49834</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82421</t>
+          <t>83369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>646137</t>
+          <t>646993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>667999</t>
+          <t>668685</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558902</t>
+          <t>557341</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>581909</t>
+          <t>582639</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1213030</t>
+          <t>1212082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1245617</t>
+          <t>1243880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>17974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39092</t>
+          <t>40953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41347</t>
+          <t>40002</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70782</t>
+          <t>68271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62905</t>
+          <t>62225</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99158</t>
+          <t>96664</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640962</t>
+          <t>639101</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663197</t>
+          <t>662080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635153</t>
+          <t>637664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>664588</t>
+          <t>665933</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1286831</t>
+          <t>1289325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1323084</t>
+          <t>1323764</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25255</t>
+          <t>25879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23590</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48625</t>
+          <t>48310</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>35269</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65373</t>
+          <t>66117</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>589362</t>
+          <t>588738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607185</t>
+          <t>607173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>565447</t>
+          <t>565762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>590482</t>
+          <t>591486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1163316</t>
+          <t>1162572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1192976</t>
+          <t>1193420</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23181</t>
+          <t>23200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14627</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33775</t>
+          <t>33251</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>411628</t>
+          <t>412330</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>424179</t>
+          <t>424169</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424619</t>
+          <t>424600</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439720</t>
+          <t>439719</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>842369</t>
+          <t>842893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>861517</t>
+          <t>861652</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23759</t>
+          <t>24180</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40494</t>
+          <t>39074</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284820</t>
+          <t>286537</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>301558</t>
+          <t>301586</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>329300</t>
+          <t>328879</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>344302</t>
+          <t>344212</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>620360</t>
+          <t>621780</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>642786</t>
+          <t>642159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>18444</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23822</t>
+          <t>23887</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36511</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230232</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244723</t>
+          <t>244661</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>361844</t>
+          <t>361779</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>378057</t>
+          <t>377991</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>598191</t>
+          <t>597904</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>619576</t>
+          <t>619255</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97114</t>
+          <t>94908</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>140864</t>
+          <t>139426</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>169425</t>
+          <t>167870</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>224957</t>
+          <t>224586</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>274781</t>
+          <t>279694</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>349313</t>
+          <t>352409</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3278324</t>
+          <t>3279762</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3322074</t>
+          <t>3324280</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3320129</t>
+          <t>3320500</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3375661</t>
+          <t>3377216</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6614961</t>
+          <t>6611865</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6689493</t>
+          <t>6684580</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>27525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>13916</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32702</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27970</t>
+          <t>27578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52348</t>
+          <t>51943</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392465</t>
+          <t>391938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>408963</t>
+          <t>409697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>363053</t>
+          <t>363540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>381383</t>
+          <t>381839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>762870</t>
+          <t>763275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>787248</t>
+          <t>787640</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13772</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31748</t>
+          <t>30707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23896</t>
+          <t>24236</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47095</t>
+          <t>46079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41916</t>
+          <t>42949</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70576</t>
+          <t>72145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>558748</t>
+          <t>559789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>576724</t>
+          <t>577038</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516449</t>
+          <t>517465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>539648</t>
+          <t>539308</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1083464</t>
+          <t>1081895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1112124</t>
+          <t>1111091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13211</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32574</t>
+          <t>34132</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59772</t>
+          <t>61222</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52170</t>
+          <t>52128</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83501</t>
+          <t>83915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636523</t>
+          <t>634965</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655886</t>
+          <t>655720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>601614</t>
+          <t>600164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>627315</t>
+          <t>626649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1246982</t>
+          <t>1246568</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1278313</t>
+          <t>1278355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22160</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22863</t>
+          <t>23062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48574</t>
+          <t>48852</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33023</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62065</t>
+          <t>61773</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>623888</t>
+          <t>624277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639138</t>
+          <t>639500</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>600503</t>
+          <t>600225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>626214</t>
+          <t>626015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1233060</t>
+          <t>1233352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1262102</t>
+          <t>1261759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29467</t>
+          <t>30075</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>17386</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39008</t>
+          <t>39516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33138</t>
+          <t>32243</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62530</t>
+          <t>60904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>448451</t>
+          <t>447843</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466728</t>
+          <t>465645</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>457841</t>
+          <t>457333</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>479998</t>
+          <t>479463</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>912237</t>
+          <t>913863</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>941629</t>
+          <t>942524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>20586</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27188</t>
+          <t>27841</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322924</t>
+          <t>323832</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332480</t>
+          <t>332489</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>357242</t>
+          <t>357176</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>371817</t>
+          <t>370896</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>684904</t>
+          <t>684251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>702065</t>
+          <t>701857</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14953</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26003</t>
+          <t>26327</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36121</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242045</t>
+          <t>241859</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>252896</t>
+          <t>252725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>374166</t>
+          <t>373842</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>391107</t>
+          <t>392234</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>621046</t>
+          <t>621944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>641529</t>
+          <t>642133</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85287</t>
+          <t>85196</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125454</t>
+          <t>126112</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>163880</t>
+          <t>165895</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>219774</t>
+          <t>218225</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>259786</t>
+          <t>262087</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>330773</t>
+          <t>332000</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3268896</t>
+          <t>3268238</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3309063</t>
+          <t>3309154</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3324768</t>
+          <t>3326317</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3380662</t>
+          <t>3378647</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6608119</t>
+          <t>6606892</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6679106</t>
+          <t>6676805</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32955</t>
+          <t>35990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22428</t>
+          <t>22149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14098</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>47460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>367032</t>
+          <t>363997</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>393517</t>
+          <t>392886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290772</t>
+          <t>291051</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309103</t>
+          <t>308541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>665187</t>
+          <t>665727</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>699089</t>
+          <t>698860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40805</t>
+          <t>39112</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>29764</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259330</t>
+          <t>266916</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52272</t>
+          <t>53209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>321557</t>
+          <t>321489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>382742</t>
+          <t>384435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>409951</t>
+          <t>410205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252174</t>
+          <t>244588</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>481298</t>
+          <t>481740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>613494</t>
+          <t>613562</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>882779</t>
+          <t>881842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30817</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>35586</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36449</t>
+          <t>36055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62419</t>
+          <t>60678</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505521</t>
+          <t>505348</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523865</t>
+          <t>524267</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>506534</t>
+          <t>506882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>522846</t>
+          <t>523292</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1016387</t>
+          <t>1018128</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1042357</t>
+          <t>1042751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49205</t>
+          <t>47958</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>31794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52965</t>
+          <t>53277</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45158</t>
+          <t>41488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93284</t>
+          <t>93418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>838581</t>
+          <t>839828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>876101</t>
+          <t>875090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>659916</t>
+          <t>659604</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681050</t>
+          <t>681087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1507383</t>
+          <t>1507249</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1555509</t>
+          <t>1559179</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>15813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31676</t>
+          <t>30993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24666</t>
+          <t>25002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43602</t>
+          <t>43362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544421</t>
+          <t>544424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>555308</t>
+          <t>555535</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>513211</t>
+          <t>513894</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>528007</t>
+          <t>527687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1061522</t>
+          <t>1061762</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1080458</t>
+          <t>1080122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27871</t>
+          <t>27941</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,47 +11435,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>23127</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>10936</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>33163</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>23127</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>11293</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>34326</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>356015</t>
+          <t>355845</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>364722</t>
+          <t>364667</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>580497</t>
+          <t>580427</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>601566</t>
+          <t>602560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,47 +11548,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>953406</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>943370</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>965597</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>98,88%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>953406</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>942207</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>965240</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11941</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>25201</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>270328</t>
+          <t>270774</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>279212</t>
+          <t>279114</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>406939</t>
+          <t>406842</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>416648</t>
+          <t>416746</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>680693</t>
+          <t>681462</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>694011</t>
+          <t>694107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84475</t>
+          <t>83532</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143314</t>
+          <t>141710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>152869</t>
+          <t>153989</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>463207</t>
+          <t>503983</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>261143</t>
+          <t>263416</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>625379</t>
+          <t>574729</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3315016</t>
+          <t>3316620</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3373855</t>
+          <t>3374798</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3194495</t>
+          <t>3153719</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3504833</t>
+          <t>3503713</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6490653</t>
+          <t>6541303</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6854889</t>
+          <t>6852616</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A08-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25471</t>
+          <t>26150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25860</t>
+          <t>27592</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24781</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46474</t>
+          <t>46855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>468593</t>
+          <t>467914</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484024</t>
+          <t>483735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>441629</t>
+          <t>439897</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>456263</t>
+          <t>456193</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>915079</t>
+          <t>914698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>936772</t>
+          <t>937318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29609</t>
+          <t>28972</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39132</t>
+          <t>37962</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31951</t>
+          <t>32056</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60253</t>
+          <t>60695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>705880</t>
+          <t>706517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>724788</t>
+          <t>724935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>586362</t>
+          <t>587532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>608397</t>
+          <t>608756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1300729</t>
+          <t>1300287</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1329031</t>
+          <t>1328926</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>21520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18992</t>
+          <t>19342</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39137</t>
+          <t>40838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29109</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53351</t>
+          <t>52830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>617718</t>
+          <t>616129</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631132</t>
+          <t>631004</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>650607</t>
+          <t>648906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>670752</t>
+          <t>670402</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1274043</t>
+          <t>1274564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1298285</t>
+          <t>1298538</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19979</t>
+          <t>20483</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25574</t>
+          <t>24490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18047</t>
+          <t>17083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41565</t>
+          <t>38880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>499168</t>
+          <t>498664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>514429</t>
+          <t>514451</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>490068</t>
+          <t>491152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>506925</t>
+          <t>506826</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>993224</t>
+          <t>995909</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1016742</t>
+          <t>1017706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12404</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30561</t>
+          <t>31435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19108</t>
+          <t>20625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41778</t>
+          <t>43629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>367149</t>
+          <t>366400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>381619</t>
+          <t>382093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>373425</t>
+          <t>372551</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>391582</t>
+          <t>391624</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>748918</t>
+          <t>747067</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>771588</t>
+          <t>770071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9226</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31873</t>
+          <t>30878</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280209</t>
+          <t>281409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290758</t>
+          <t>291157</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>318445</t>
+          <t>316919</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>333708</t>
+          <t>333178</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>603644</t>
+          <t>604639</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>621736</t>
+          <t>622403</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23387</t>
+          <t>21718</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>198464</t>
+          <t>199280</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208247</t>
+          <t>208172</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>317607</t>
+          <t>318174</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330644</t>
+          <t>330639</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>520404</t>
+          <t>522073</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>537129</t>
+          <t>537995</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61076</t>
+          <t>61806</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96429</t>
+          <t>97361</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110391</t>
+          <t>112128</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>157218</t>
+          <t>156802</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>182254</t>
+          <t>181916</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>242954</t>
+          <t>238183</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3179096</t>
+          <t>3178164</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3214449</t>
+          <t>3213719</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3221979</t>
+          <t>3222395</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3268806</t>
+          <t>3267069</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6411768</t>
+          <t>6416539</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6472468</t>
+          <t>6472806</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28148</t>
+          <t>28297</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19198</t>
+          <t>18444</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39258</t>
+          <t>39623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>33085</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60975</t>
+          <t>59993</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424957</t>
+          <t>424808</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>441942</t>
+          <t>441644</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390081</t>
+          <t>389716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>410141</t>
+          <t>410895</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>821470</t>
+          <t>822452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>848397</t>
+          <t>849360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39245</t>
+          <t>38679</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51873</t>
+          <t>51086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51571</t>
+          <t>50482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83369</t>
+          <t>83478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>646993</t>
+          <t>647559</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>668685</t>
+          <t>668903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>557341</t>
+          <t>558128</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>582639</t>
+          <t>582022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1212082</t>
+          <t>1211973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1243880</t>
+          <t>1244969</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40953</t>
+          <t>41691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40002</t>
+          <t>39754</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68271</t>
+          <t>68137</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62225</t>
+          <t>63571</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96664</t>
+          <t>98726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>639101</t>
+          <t>638363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662080</t>
+          <t>661833</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637664</t>
+          <t>637798</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>665933</t>
+          <t>666181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1289325</t>
+          <t>1287263</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1323764</t>
+          <t>1322418</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25879</t>
+          <t>27304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48310</t>
+          <t>48398</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35269</t>
+          <t>35861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66117</t>
+          <t>64611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>588738</t>
+          <t>587313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607173</t>
+          <t>607309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>565762</t>
+          <t>565674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>591486</t>
+          <t>589912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1162572</t>
+          <t>1164078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1193420</t>
+          <t>1192828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>23450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33251</t>
+          <t>32553</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>412330</t>
+          <t>413058</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>424169</t>
+          <t>424207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424600</t>
+          <t>424350</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439719</t>
+          <t>439572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>842893</t>
+          <t>843591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>861652</t>
+          <t>861807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21258</t>
+          <t>21731</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>23801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18695</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39074</t>
+          <t>39345</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286537</t>
+          <t>286064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>301586</t>
+          <t>300841</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>328879</t>
+          <t>329258</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>344212</t>
+          <t>344432</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>621780</t>
+          <t>621509</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>642159</t>
+          <t>642433</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18444</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>8608</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23887</t>
+          <t>23219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15447</t>
+          <t>15976</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>35209</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>230858</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244661</t>
+          <t>244851</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>361779</t>
+          <t>362447</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>377991</t>
+          <t>377058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>597904</t>
+          <t>599493</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>619255</t>
+          <t>618726</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94908</t>
+          <t>95064</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>139426</t>
+          <t>139924</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>167870</t>
+          <t>167255</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>224586</t>
+          <t>223801</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>279694</t>
+          <t>278194</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>352409</t>
+          <t>348033</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3279762</t>
+          <t>3279264</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3324280</t>
+          <t>3324124</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3320500</t>
+          <t>3321285</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3377216</t>
+          <t>3377831</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6611865</t>
+          <t>6616241</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6684580</t>
+          <t>6686080</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27525</t>
+          <t>26668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32215</t>
+          <t>32581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27578</t>
+          <t>27661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51943</t>
+          <t>52052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391938</t>
+          <t>392795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>409697</t>
+          <t>408678</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>363540</t>
+          <t>363174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>381839</t>
+          <t>381348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>763275</t>
+          <t>763166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>787640</t>
+          <t>787557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30707</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24236</t>
+          <t>25334</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46079</t>
+          <t>47999</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42949</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72145</t>
+          <t>71880</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>559789</t>
+          <t>559725</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>577038</t>
+          <t>577217</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>517465</t>
+          <t>515545</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>539308</t>
+          <t>538210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1081895</t>
+          <t>1082160</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1111091</t>
+          <t>1111640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>12278</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34132</t>
+          <t>32004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>34508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61222</t>
+          <t>59180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52128</t>
+          <t>51898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83915</t>
+          <t>86098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>634965</t>
+          <t>637093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655720</t>
+          <t>656819</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>600164</t>
+          <t>602206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>626649</t>
+          <t>626878</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1246568</t>
+          <t>1244385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1278355</t>
+          <t>1278585</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21771</t>
+          <t>23497</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23062</t>
+          <t>23364</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48852</t>
+          <t>49320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33366</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>61177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>624277</t>
+          <t>622551</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639500</t>
+          <t>639300</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>600225</t>
+          <t>599757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>626015</t>
+          <t>625713</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1233352</t>
+          <t>1233948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1261759</t>
+          <t>1262357</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12273</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>30438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17386</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39516</t>
+          <t>40727</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32243</t>
+          <t>32417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60904</t>
+          <t>60494</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>447843</t>
+          <t>447480</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465645</t>
+          <t>465917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>457333</t>
+          <t>456122</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>479463</t>
+          <t>479147</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>913863</t>
+          <t>914273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>942524</t>
+          <t>942350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>21406</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27841</t>
+          <t>27108</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323832</t>
+          <t>323772</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332489</t>
+          <t>332454</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>357176</t>
+          <t>356356</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>370896</t>
+          <t>371370</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>684251</t>
+          <t>684984</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>701857</t>
+          <t>701963</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15139</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26327</t>
+          <t>26208</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15034</t>
+          <t>16075</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>36782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>241859</t>
+          <t>242180</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>252725</t>
+          <t>252909</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>373842</t>
+          <t>373961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>392234</t>
+          <t>391067</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>621944</t>
+          <t>620385</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>642133</t>
+          <t>641092</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85196</t>
+          <t>87399</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126112</t>
+          <t>125072</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>165895</t>
+          <t>163853</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>218225</t>
+          <t>221970</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>262087</t>
+          <t>261314</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>332000</t>
+          <t>327835</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3268238</t>
+          <t>3269278</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3309154</t>
+          <t>3306951</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3326317</t>
+          <t>3322572</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3378647</t>
+          <t>3380689</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6606892</t>
+          <t>6611057</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6676805</t>
+          <t>6677578</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35990</t>
+          <t>27398</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22149</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>26420</t>
+          <t>28280</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47460</t>
+          <t>45976</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>383791</t>
+          <t>394104</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>363997</t>
+          <t>380395</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392886</t>
+          <t>402271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>302976</t>
+          <t>347922</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291051</t>
+          <t>334559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308541</t>
+          <t>356120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>686767</t>
+          <t>742025</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>665727</t>
+          <t>724329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>698860</t>
+          <t>754072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23947</t>
+          <t>23884</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39112</t>
+          <t>37812</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>99044</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29764</t>
+          <t>23035</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>266916</t>
+          <t>48603</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>122991</t>
+          <t>57648</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53209</t>
+          <t>43233</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>321489</t>
+          <t>78004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399600</t>
+          <t>453006</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384435</t>
+          <t>439078</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410205</t>
+          <t>463054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>412460</t>
+          <t>467319</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>244588</t>
+          <t>452480</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>481740</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>812060</t>
+          <t>920325</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>613562</t>
+          <t>899969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>881842</t>
+          <t>934740</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>23320</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>35464</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26656</t>
+          <t>30654</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35586</t>
+          <t>41180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46908</t>
+          <t>53973</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36055</t>
+          <t>40756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60678</t>
+          <t>68479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>516086</t>
+          <t>597517</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505348</t>
+          <t>585373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524267</t>
+          <t>606132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>515812</t>
+          <t>591485</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>506882</t>
+          <t>580959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>523292</t>
+          <t>599731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1031898</t>
+          <t>1189003</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1018128</t>
+          <t>1174497</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1042751</t>
+          <t>1202220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29965</t>
+          <t>33548</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47958</t>
+          <t>46901</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>47507</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31794</t>
+          <t>37964</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53277</t>
+          <t>59628</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>71832</t>
+          <t>81055</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41488</t>
+          <t>67343</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93418</t>
+          <t>100493</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>857821</t>
+          <t>667069</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>839828</t>
+          <t>653716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>875090</t>
+          <t>677977</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>671014</t>
+          <t>689379</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>659604</t>
+          <t>677258</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681087</t>
+          <t>698922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1528835</t>
+          <t>1356449</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1507249</t>
+          <t>1337011</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1559179</t>
+          <t>1370161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23732</t>
+          <t>26329</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17200</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>35925</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>32865</t>
+          <t>36973</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25002</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43362</t>
+          <t>47867</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>551104</t>
+          <t>597715</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544424</t>
+          <t>589318</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>555535</t>
+          <t>602960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>521155</t>
+          <t>581119</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>513894</t>
+          <t>571523</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>527687</t>
+          <t>588516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1072259</t>
+          <t>1178834</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1061762</t>
+          <t>1167940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1080122</t>
+          <t>1188407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16394</t>
+          <t>18584</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27941</t>
+          <t>25641</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>25940</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33163</t>
+          <t>33885</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>361432</t>
+          <t>399724</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>355845</t>
+          <t>393780</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>364667</t>
+          <t>403376</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>591974</t>
+          <t>420582</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>580427</t>
+          <t>413525</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>602560</t>
+          <t>425797</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>953406</t>
+          <t>820306</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>943370</t>
+          <t>812361</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>965597</t>
+          <t>827032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,17 +11723,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>12830</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>20597</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25201</t>
+          <t>29050</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -11836,17 +11836,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>275815</t>
+          <t>302599</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>270774</t>
+          <t>296873</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>279114</t>
+          <t>306066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>412630</t>
+          <t>449586</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>406842</t>
+          <t>443337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>416746</t>
+          <t>454566</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>688445</t>
+          <t>752185</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>681462</t>
+          <t>743732</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>694107</t>
+          <t>758474</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>112679</t>
+          <t>119545</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83532</t>
+          <t>99673</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>141710</t>
+          <t>146731</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>229682</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>153989</t>
+          <t>162551</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>503983</t>
+          <t>211185</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>342361</t>
+          <t>304467</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>263416</t>
+          <t>273514</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>574729</t>
+          <t>339927</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3345651</t>
+          <t>3411735</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3316620</t>
+          <t>3384549</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3374798</t>
+          <t>3431607</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3428020</t>
+          <t>3547392</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3153719</t>
+          <t>3521128</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3503713</t>
+          <t>3569762</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6773671</t>
+          <t>6959126</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6541303</t>
+          <t>6923666</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6852616</t>
+          <t>6990079</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
